--- a/testes/silicone_smf_5pontos/dados.xlsx
+++ b/testes/silicone_smf_5pontos/dados.xlsx
@@ -1888,49 +1888,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1.362049432820595</v>
+        <v>0.5423957977920935</v>
       </c>
       <c r="B31" t="n">
-        <v>2.327602666718221</v>
+        <v>0.6319431058390622</v>
       </c>
       <c r="C31" t="n">
-        <v>2.836064329555581</v>
+        <v>0.5486717051206486</v>
       </c>
       <c r="D31" t="n">
-        <v>3.605180228934399</v>
+        <v>0.8732682520279779</v>
       </c>
       <c r="E31" t="n">
-        <v>4.462755118865098</v>
+        <v>0.6621963455048659</v>
       </c>
       <c r="F31" t="n">
-        <v>5.199296393080461</v>
+        <v>0.7879381701631158</v>
       </c>
       <c r="G31" t="n">
-        <v>5.957241151552882</v>
+        <v>1.438981528720921</v>
       </c>
       <c r="H31" t="n">
-        <v>6.606291298308927</v>
+        <v>1.68592260795091</v>
       </c>
       <c r="I31" t="n">
-        <v>7.269540314288014</v>
+        <v>1.088762802450561</v>
       </c>
       <c r="J31" t="n">
-        <v>7.82573757689644</v>
+        <v>1.424372760200082</v>
       </c>
       <c r="K31" t="n">
-        <v>8.380937332736423</v>
+        <v>1.035434131173973</v>
       </c>
       <c r="L31" t="n">
-        <v>9.167754376128343</v>
+        <v>2.273537015313364</v>
       </c>
       <c r="M31" t="n">
-        <v>9.756382385392651</v>
+        <v>1.542347094528336</v>
       </c>
       <c r="N31" t="n">
-        <v>10.44433129769727</v>
+        <v>1.418913161543017</v>
       </c>
       <c r="O31" t="n">
-        <v>11.0669386646969</v>
+        <v>1.343007133264749</v>
       </c>
     </row>
   </sheetData>
